--- a/artfynd/A 19145-2026 artfynd.xlsx
+++ b/artfynd/A 19145-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114569228</v>
+        <v>81760769</v>
       </c>
       <c r="B2" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fallviken-Grönviken, Gstr</t>
+          <t>Åmot, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570978</v>
+        <v>571344</v>
       </c>
       <c r="R2" t="n">
-        <v>6765184</v>
+        <v>6765104</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,12 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2019-08-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2019-08-28</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Ecocom AB</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -763,66 +759,55 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mårten Nilsson</t>
+          <t>Axel Linder</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Barbara Kühn, Kajsa Mattsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114566352</v>
+        <v>114564814</v>
       </c>
       <c r="B3" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -830,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571438</v>
+        <v>571351</v>
       </c>
       <c r="R3" t="n">
-        <v>6765067</v>
+        <v>6765091</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -863,9 +848,19 @@
           <t>2023-09-27</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,10 +881,218 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>114566352</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Fallviken-Grönviken, Gstr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>571438</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6765067</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mårten Nilsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
           <t>Veronica Lindström</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>114569228</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Fallviken-Grönviken, Gstr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>570978</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6765184</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mårten Nilsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
